--- a/medford_kholedokhoskopy.xlsx
+++ b/medford_kholedokhoskopy.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Холедохоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Pentax, Olympus — всего 3 позиций.</t>
+          <t>Холедохоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Pentax, Olympus.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_kholedokhoskopy.xlsx
+++ b/medford_kholedokhoskopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать холедохоскопы для клиники?</t>
+          <t>Чем холедохоскоп отличается от дуоденоскопа?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диаметр дистального конца, мм, Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Холедохоскоп предназначен для осмотра просвета самих желчных протоков изнутри и манипуляций в них под контролем зрения. Дуоденоскоп осматривает двенадцатиперстную кишку и область большого дуоденального сосочка. Их применяют на разных этапах: дуоденоскоп — для доступа, холедохоскоп — для работы непосредственно в протоке.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Гибкий или жёсткий холедохоскоп выбрать?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Гибкие модели проходят по извитым участкам протока за счёт управляемого дистального конца и удобны для диагностики и малоинвазивных манипуляций. Жёсткие применяют при сложных хирургических операциях, где нужна максимальная точность и стабильность позиционирования. Все три модели каталога — гибкие фиброскопы. Выбор под клиническую задачу определяет врач.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что означает угол обзора в воде?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Pentax, Olympus. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Холедохоскопия часто идёт при ирригации протока жидкостью, а в воде угол поля зрения меняется из-за иной оптической среды. Поэтому у моделей Pentax указывают два значения: 125°/83° у FCN-15X и 90°/64° у FCP-9P. Второе число отражает реальный обзор во время процедуры в жидкой среде.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Можно ли извлекать камни холедохоскопом?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Да, под зрительным контролем через инструментальный канал холедохоскопа выполняют удаление мелких конкрементов, а также биопсию и установку стентов. Возможность и объём вмешательства зависят от размера конкремента, диаметра протока и оснащения. Показания и тактику определяет оперирующий врач.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Как проверить совместимость со стойкой?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Сверяют тип разъёма холедохоскопа с источником света, а для видеомоделей — с видеопроцессором отделения. Волоконные фиброскопы требуют совместимого осветителя, видеосистемы — процессора своей платформы. Точные требования указывает производитель в спецификации; их проверяют до покупки, чтобы не докупать блоки отдельно.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Медицинское изделие вводят в оборот в России при наличии действующего регистрационного удостоверения Росздравнадзора на конкретную модель. Перед приобретением уточняют статус РУ, а также наличие расходников и условия сервиса. Это часть проверки, а не формальность: без РУ эксплуатация в клинике невозможна.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>kholedokhoskopy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Какой диаметр дистального конца выбрать?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>У моделей каталога диаметр составляет 3,0–4,8 мм. Тонкий конец проходит в узкий проток и меньше травмирует стенку, но ограничивает канал для инструментов. Более толстый даёт запас по функционалу. Оптимальное соотношение под конкретную анатомию и задачи определяет врач по клинической ситуации.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>kholedokhoskopy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Холедохоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Pentax, Olympus.</t>
+          <t>Холедохоскоп — эндоскоп для прямого визуального исследования внепечёночных желчных протоков и малоинвазивных манипуляций в них под зрительным контролем. В каталоге представлены гибкие холедохофиброскопы Pentax и Olympus с диаметром дистального конца от 3,0 до 4,8 мм и рабочей длиной от 350 до 1900 мм. Тонкий дистальный конец и глубина резкости 1–50 мм позволяют работать в узком просвете протока. Угол поля зрения моделей — 90–125°, у части моделей отдельно нормируется обзор в воде.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы холедохоскопов</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое холедохоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3101,155 +3177,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы холедохоскопов</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Гибкий фиброскоп</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр дистального конца, мм</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр вводимой трубки, мм</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Глубина резкости, мм</t>
+          <t>Видео/жёсткий</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Холедохофиброскоп Pentax FCN-15X</t>
+          <t>Носитель изображения</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>волоконная оптика</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>3-50</t>
+          <t>видеоматрица или прямая оптика</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Холедохофиброскоп Olympus CHF-BP30</t>
+          <t>Основное применение</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>диагностика, малоинвазивные манипуляции</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1-50</t>
+          <t>сложные хирургические операции, документирование</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Холедохофиброскоп Pentax FCP-9P</t>
+          <t>Доступ к извитым участкам</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>высокий за счёт ангуляции</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1-50</t>
+          <t>ограничен у жёстких</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Модели каталога</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Pentax FCN-15X, FCP-9P, Olympus CHF-BP30</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>в каталоге не представлены</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3261,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3587,12 +3617,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип доступа</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается холедохоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала уточняют, как холедохоскоп будет вводиться: интраоперационно через открытый или лапароскопический доступ либо трансдуоденально. От этого зависит нужная рабочая длина — короткие модели около 350 мм для прямого доступа к протоку и длинные до 1900 мм для трансдуоденального проведения. Ошибка на этом шаге делает остальные характеристики второстепенными.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3632,12 +3662,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Сопоставьте диаметр с протоком</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Диаметр дистального конца у моделей каталога составляет от 3,0 до 4,8 мм. Тонкий конец проходит в узкий или суженный проток, но ограничивает размер инструментального канала. Выбор диаметра под анатомию конкретных пациентов и планируемые манипуляции определяет врач; технически задача — обеспечить проходимость без избыточной травматизации стенки.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3677,12 +3707,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените глубину резкости и угол обзора</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диаметр дистального конца, мм, Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Глубина резкости у моделей — 1–50 мм, угол поля зрения — 90–125°, у Pentax отдельно указан обзор в воде (83° и 64°). Широкий угол и большая глубина резкости дают полную картину стенки протока и облегчают навигацию к конкременту. Для процедур в жидкой среде важен именно параметр обзора в воде.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3722,12 +3752,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Выберите носитель изображения</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Pentax, Olympus.</t>
+          <t>Холедохофиброскоп строит изображение на волоконной оптике, видеохоледохоскоп — на матрице с выводом на монитор. Волоконные модели компактнее и автономнее, видеосистемы дают более высокое разрешение и удобны для документирования. Все три позиции каталога — гибкие фиброскопы, что подходит для диагностики и малоинвазивных манипуляций.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3767,12 +3797,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте совместимость с системой</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Холедохоскоп работает в связке с источником света и, для видеомоделей, с видеопроцессором. До приобретения сверяют тип разъёма и совместимость с уже имеющейся стойкой отделения. Несовпадение платформы означает докупку блоков, поэтому совместимость проверяют по спецификации производителя заранее.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3812,12 +3842,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните регистрацию и обслуживание</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Перед вводом в оборот проверяют наличие действующего регистрационного удостоверения Росздравнадзора на конкретную модель. Отдельно уточняют доступность расходников, ремонтопригодность оптоволоконного жгута и условия сервисной поддержки — у тонких гибких эндоскопов рабочий канал и жгут волокон относятся к наиболее нагруженным узлам.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3867,7 +3897,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Холедохоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Pentax, Olympus. При выборе обращают внимание на диаметр дистального конца, диаметр вводимой трубки, рабочая длина, глубина резкости, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>При выборе холедохоскопа первично соотношение диаметра дистального конца и просвета протока: слишком толстый конец не пройдёт в узкий холедох. Дальше смотрю на рабочую длину под конкретный доступ — трансдуоденальный или интраоперационный — и на глубину резкости, от неё зависит, насколько уверенно видно стенку и конкремент. Волоконный фиброскоп и видеохоледохоскоп решают разные задачи, и совместимость со стойкой проверяю до покупки, а не после.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4151,13 +4181,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое холедохоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Холедохоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Pentax, Olympus. Подберём вариант под задачи вашего отделения.</t>
+          <t>Холедохоскоп применяют для осмотра общего желчного протока и манипуляций в нём: извлечения мелких конкрементов, биопсии и установки стентов под контролем зрения. Гибкие фиброскопы Pentax FCN-15X, Pentax FCP-9P и Olympus CHF-BP30 различаются диаметром дистального конца (от 3,0 до 4,8 мм), рабочей длиной (от 350 до 1900 мм), глубиной резкости (1–50 мм) и углом обзора (90–125°). При подборе смотрят на диаметр относительно просвета протока, рабочую длину под тип доступа и совместимость с имеющейся эндоскопической стойкой и источником света. Целесообразность процедуры определяет врач.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4194,13 +4224,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое холедохоскоп</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диаметр дистального конца, мм, Диаметр вводимой трубки, мм, Рабочая длина, мм, Глубина резкости, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Холедохоскоп — специализированный эндоскоп для прямого осмотра внепечёночных желчных протоков и малоинвазивных манипуляций в них. Прибор сочетает оптическую систему с гибкой конструкцией, что позволяет проводить осмотр стенки протока, выявлять конкременты, стриктуры и новообразования, а также выполнять биопсию и извлечение мелких камней под контролем зрения.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4237,13 +4267,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Ключевые характеристики</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные параметры холедохоскопа — диаметр дистального конца и вводимой трубки, рабочая длина, глубина резкости и угол поля зрения. В каталоге диаметр дистального конца составляет 3,0–4,8 мм, рабочая длина — 350–1900 мм, глубина резкости — 1–50 мм, угол обзора — 90–125°. Эти значения задают проходимость и качество визуализации.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4280,13 +4310,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды холедохоскопов</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Приборы делят по конструкции на гибкие и жёсткие, а по типу изображения — на холедохофиброскопы с волоконной оптикой и видеохоледохоскопы с видеоматрицей. Гибкие фиброскопы удобны для диагностики и малоинвазивных процедур, жёсткие — для сложных операций. Все три позиции каталога относятся к гибким холедохофиброскопам.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4303,6 +4333,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Совместимость и эксплуатация</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Холедохоскоп работает в связке с источником света, а видеомодели — с видеопроцессором. Перед приобретением сверяют тип разъёма и платформу с оснащением отделения, проверяют регистрационное удостоверение и доступность расходников. У тонких гибких эндоскопов оптоволоконный жгут и рабочий канал относятся к нагруженным узлам и требуют аккуратного обращения.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>kholedokhoskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
